--- a/excel_data/GetInTouch.xlsx
+++ b/excel_data/GetInTouch.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,9 +433,524 @@
         <v>jbkhgytfr</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Arpit Singh</v>
+      </c>
+      <c r="B3" t="str">
+        <v>arpitsin28@gmail.com</v>
+      </c>
+      <c r="C3" t="str">
+        <v>09473733115</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Cadastral Datasets, Land Record Verification</v>
+      </c>
+      <c r="E3" t="str">
+        <v>jkhyguf</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Arpit Singh</v>
+      </c>
+      <c r="B4" t="str">
+        <v>arpitsin28@gmail.com</v>
+      </c>
+      <c r="C4" t="str">
+        <v>09473733115</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Land Record Verification, Cadastral Datasets</v>
+      </c>
+      <c r="E4" t="str">
+        <v>uhiyuf</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>QGIS</v>
+      </c>
+      <c r="B5" t="str">
+        <v>jalindarjk12@gmail.com</v>
+      </c>
+      <c r="C5" t="str">
+        <v>9028052828</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Land Record Verification, Cadastral Datasets</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Priya Alisha</v>
+      </c>
+      <c r="B6" t="str">
+        <v>priyaalisha10ju@gmail.com</v>
+      </c>
+      <c r="C6" t="str">
+        <v>08541095630</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Data Cleaning, Data Correction</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
+      <c r="A7" t="str">
+        <v>Prakash namdeo Gaikwad</v>
+      </c>
+      <c r="B7" t="str">
+        <v>gaikwadprakash27761@gmail.com</v>
+      </c>
+      <c r="C7" t="str">
+        <v>7211153627</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear sir/mam
+i have done all india travel of @2lakh km. i am in process of writing a book on that. i am seeking tourist maps of @ 200 cities from all over india.
+yours sincerely
+prakash n gaikwad
+BE civil with more than 30 years of experience.</v>
+      </c>
+    </row>
+    <row r="8" xml:space="preserve">
+      <c r="A8" t="str">
+        <v>Hannah Barnes</v>
+      </c>
+      <c r="B8" t="str">
+        <v>hbarnes180@outlook.com</v>
+      </c>
+      <c r="C8" t="str">
+        <v>733-230-4798</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str" xml:space="preserve">
+        <v xml:space="preserve">Quick note-- "been" might need checking. I've used spellpros.com effectively for these.
+Thanks,
+Hannah</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>wVsATTyipPNCH</v>
+      </c>
+      <c r="B9" t="str">
+        <v>otudevimi12@gmail.com</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2836416439</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Land Record Verification, Cadastral Datasets</v>
+      </c>
+      <c r="E9" t="str">
+        <v>QjfDlAEP</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v xml:space="preserve">Anamika patel </v>
+      </c>
+      <c r="B10" t="str">
+        <v>anamikaptel6879@gmail.com</v>
+      </c>
+      <c r="C10" t="str">
+        <v>9243607961</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E10" t="str">
+        <v>I hope you are doing well.I am writing to express my interest in the software engineer position at your Company . I have recently completed my B.Tech in Computer Science and have skills inJava, React.js, and SAP ABAP. I would be grateful for the opportunity to discuss how my background and enthusiasm align with your team’s needs.Thank you for your time and consideration.Warm regards</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>Kedar Mahesh Kamble -Teli</v>
+      </c>
+      <c r="B11" t="str">
+        <v>kedarkamble007@gmail.com</v>
+      </c>
+      <c r="C11" t="str">
+        <v>8308786568</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E11" t="str" xml:space="preserve">
+        <v xml:space="preserve">I am an Software Developer with 2 years 6 months of hands on real project experience in Angular (HTML 5 + CSS 3) +PHP+MySQL Tech stack. Interested for work and grow in Nodejs technology.
+Appreciate to connect for further discussion.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Roshni Surywanshi</v>
+      </c>
+      <c r="B12" t="str">
+        <v>roshnisurywanshi012@gmail.com</v>
+      </c>
+      <c r="C12" t="str">
+        <v>7498271283</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>Mayank Yadav</v>
+      </c>
+      <c r="B13" t="str">
+        <v>mayankmditm@gmail.com</v>
+      </c>
+      <c r="C13" t="str">
+        <v>9229849956</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E13" t="str" xml:space="preserve">
+        <v xml:space="preserve"> 
+Dear HR,
+Greetings from Patel Group of Institutions – INDORE (MP)
+It gives me immense pleasure to invite your esteemed Organization for campus recruitment of final year graduates and postgraduate students for the session 2025 -26 at PGOI – INDORE (MP). Campus recruitment is a platform to provide the best match between the student's aspirations and your requirements.
+The institute has successfully provided highly talented young engineers and scientists to the nation, who were and are serving India in all sectors; Govt., Public, Private, and NGOs. They occupy key positions in industry, government, and education in India and abroad. We can give 400 Computers for the online Exam &amp; 300 seating capacity AC Auditorium for campus drive.
+List of institutions with Branch intake 
+PATEL COLLEGE OF SCIENCE &amp; TECHNOLOGY (PCST), INDORE
+Diploma (CE/CSE/EE/ME) B.Tech. (CE/CSE/CSE-AIML/CSE-IOT &amp; CS/ECE/ME) M.Tech. (CSE/IT/SS/DC/VLSI/Thermal) MBA (HR/Marketing/Finance/IT/BA/POM) MCA
+PATEL COLLEGE OF MANAGEMENT (PCM), INDORE
+MBA (HR/Marketing/Finance/IT/BA/POM)
+PATEL COLLEGE OF PHARMACY (PCP), INDORE
+D.Pharma B.Pharma
+PATEL COLLEGE OF SCIENCE &amp; TECHNOLOGY (PCST), BHOPAL
+B.Tech.: ECE/CSE/ME/AI &amp; ML/Data Science, M.Tech.:-CSE/DC/SS/TH, Polytechnic ME/CSE/EC/IT/EE/Civil, MCA, Diploma: CSE (Working Professionals) Part time
+ You can send me JD or fill out the attached Job Announcement Form (JAF) for your kind perusal. You are requested to duly filled-in a form for us to fix a mutually convenient date for your visit to our campus. For further information kindly fill out the G-Form visit https://goo.gl/forms/gBzikZ9UhLTtJF002
+As you also know, the training and placement process is not just a once-in-a-year association but a long-term one, which may lead to future industry-academia collaboration at a higher level in the form of joint R&amp;D projects, mutual exchange visits, two-ways technical seminars, etc., I am sure that the association between a reputed organization like yours and an academic institute of excellence like ours will create synergies, which have never existed before. 
+If you have any queries, please get in touch with Mayank Yadav (+91- 9229849956).
+</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v xml:space="preserve">Swapnil Prakash Shinde </v>
+      </c>
+      <c r="B14" t="str">
+        <v>swshinde07@gmail.com</v>
+      </c>
+      <c r="C14" t="str">
+        <v>7498010349</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v xml:space="preserve">Joyston Francis Rodrigues </v>
+      </c>
+      <c r="B15" t="str">
+        <v>joystonrodrigues16@gmail.com</v>
+      </c>
+      <c r="C15" t="str">
+        <v>8296839379</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Land Record Verification</v>
+      </c>
+      <c r="E15" t="str">
+        <v xml:space="preserve">As final year Engineering Student studying in Mangalore Karnataka, wanted to apply for the Internship in your company </v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
+        <v>JAMADAR NILOFAR SARDAR</v>
+      </c>
+      <c r="B16" t="str">
+        <v>jamadarn380@gmail.com</v>
+      </c>
+      <c r="C16" t="str">
+        <v>8983937011</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E16" t="str" xml:space="preserve">
+        <v xml:space="preserve">Subject: Internship Opportunity Inquiry
+Respected Sir/Madam,
+I hope this message finds you well. I am Nilofar Sardar Jamadar, as a committed Postgraduate MSc in Geography in Shivaji University Kolhapur currently advancing studies with an MTech in Geoinformatics in University of Madras. and I am very interested in gaining practical experience in the field. I would like to inquire if there are any internship opportunities available at PFEPL, where I can apply and further develop my skills.
+I am eager to contribute to your team and learn from the expertise at your esteemed organization. Please let me know the process for applying or if any additional information is required.
+Thank you for considering my request. I look forward to your positive response.
+ Your Sincerely,
+NILOFAR SARDAR JAMADAR
+jamadarn380@gmail.com 
+8983937011
+</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Niyoshka Pereira</v>
+      </c>
+      <c r="B17" t="str">
+        <v>niyomaria@rediffmail.com</v>
+      </c>
+      <c r="C17" t="str">
+        <v>08605297854</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Exploring opportunities for GIS</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>nYyUZFKkSBPfUoZqaNT</v>
+      </c>
+      <c r="B18" t="str">
+        <v>mayateyoxap60@gmail.com</v>
+      </c>
+      <c r="C18" t="str">
+        <v>4988483251</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Cadastral Datasets, Data Cleaning</v>
+      </c>
+      <c r="E18" t="str">
+        <v>tQhdtTRYZFmyblTCmOKp</v>
+      </c>
+    </row>
+    <row r="19" xml:space="preserve">
+      <c r="A19" t="str">
+        <v>Anurag Paliwal</v>
+      </c>
+      <c r="B19" t="str">
+        <v>anuragpaliwal65@gmail.com</v>
+      </c>
+      <c r="C19" t="str">
+        <v>9410778759</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E19" t="str" xml:space="preserve">
+        <v xml:space="preserve">Hello,
+I am interested in GIS Intern opportunities and would like to know the appropriate contact to submit my resume and cover letter.
+Thank you.
+Anurag Paliwal</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Tanush Garg</v>
+      </c>
+      <c r="B20" t="str">
+        <v>tanush.garg@ci-metrics.com</v>
+      </c>
+      <c r="C20" t="str">
+        <v>9116604259</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Cadastral Datasets</v>
+      </c>
+      <c r="E20" t="str">
+        <v>We would like to connect with your team for your API services.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Roshni Surywanshi</v>
+      </c>
+      <c r="B21" t="str">
+        <v>roshnisurywanshi012@gmail.com</v>
+      </c>
+      <c r="C21" t="str">
+        <v>7498271283</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>ABHISHEK SHIVAJI NAGARE</v>
+      </c>
+      <c r="B22" t="str">
+        <v>abhinagare2003@gmail.com</v>
+      </c>
+      <c r="C22" t="str">
+        <v>9850016131</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E22" t="str" xml:space="preserve">
+        <v xml:space="preserve">Dear Sir/Madam,
+I am writing to apply for the position of Agricultural Engineer in your esteemed organization. I have completed my B.Tech in Agricultural Engineering from Dr. A.S. College of Agricultural Engineering &amp; Technology, Rahuri, with a CGPA of 7.1/10. I possess hands-on experience in soil survey, farm machinery testing, irrigation engineering, and meteorological data analysis.
+During my internship at ICAR–National Bureau of Soil Survey and Land Use Planning, Nagpur, I assisted in soil classification, land-use mapping, and geospatial analysis using ArcGIS. My training at the India Meteorological Department, Pune, enhanced my analytical skills in weather-based agricultural planning. Additionally, at the Central Farm Machinery Training and Testing Institute, Budhni, I gained practical exposure to farm machinery testing and performance evaluation.
+I am proficient in MS Office, Excel data handling, and AutoCAD basics. With strong teamwork, leadership, and communication skills, I am confident in contributing effectively to your organization’s technical and field operations.
+I would welcome the opportunity to discuss how my skills align with your requirements.
+Thanking you.
+Yours sincerely,
+Abhishek Shivaji Nagare</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
+        <v>Roshni Surywanshi</v>
+      </c>
+      <c r="B23" t="str">
+        <v>roshnisurywanshi012@gmail.com</v>
+      </c>
+      <c r="C23" t="str">
+        <v>7498271283</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E23" t="str" xml:space="preserve">
+        <v xml:space="preserve">My name is Roshni. I have completed my training in GIS and I am looking for a fresher opportunity.
+I have worked on projects like base mapping, road centerline digitization, EOP and point features using ArcGIS Pro.
+I have basic knowledge of digitization, georeferencing, and data quality checking.
+I would be grateful if you consider me for any suitable GIS fresher position.</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
+        <v>Sahana J</v>
+      </c>
+      <c r="B24" t="str">
+        <v>sahanakhan220@gmail.com</v>
+      </c>
+      <c r="C24" t="str">
+        <v>7975292310</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Others</v>
+      </c>
+      <c r="E24" t="str" xml:space="preserve">
+        <v xml:space="preserve">I'm Sahana J 
+     I'm looking for a job if any vacancy is there then please let me know </v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
+        <v>Suvosree Roy</v>
+      </c>
+      <c r="B25" t="str">
+        <v>info@digitalindian.co.in</v>
+      </c>
+      <c r="C25" t="str">
+        <v>9030080679</v>
+      </c>
+      <c r="D25" t="str">
+        <v>Cadastral Datasets, Land Record Verification, Data Cleaning, Data Correction, Others</v>
+      </c>
+      <c r="E25" t="str" xml:space="preserve">
+        <v xml:space="preserve">I hope this message finds you well.
+I am writing on behalf of DigitalIndian Business Solutions Pvt. Ltd., a growing technology and consulting firm specializing in Geographic Information Systems (GIS), data management, and IT-enabled services.
+With the GIS industry witnessing rapid growth in India, the demand for high-precision spatial data, mapping, and decision-support solutions continues to rise. We understand the critical importance of accuracy and reliability in GIS deliverables, particularly across sectors such as urban planning, transportation, infrastructure, utilities, environmental management, and e-governance.
+At Digital Indian Business Solutions, we take pride in consistently achieving over 80% accuracy in GIS data processing, feature extraction, mapping, and quality-controlled deliverables. This is supported by our robust quality assurance framework, experienced professionals, and the use of advanced GIS tools and technologies.</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>Suvosree Roy</v>
+      </c>
+      <c r="B26" t="str">
+        <v>info@digitalindian.co.in</v>
+      </c>
+      <c r="C26" t="str">
+        <v>9030080679</v>
+      </c>
+      <c r="D26" t="str">
+        <v>Cadastral Datasets, Land Record Verification, Data Cleaning, Data Correction, Others</v>
+      </c>
+      <c r="E26" t="str" xml:space="preserve">
+        <v xml:space="preserve">I hope this message finds you well.
+I am writing on behalf of DigitalIndian Business Solutions Pvt. Ltd., a growing technology and consulting firm specializing in Geographic Information Systems (GIS), data management, and IT-enabled services.
+With the GIS industry witnessing rapid growth in India, the demand for high-precision spatial data, mapping, and decision-support solutions continues to rise. We understand the critical importance of accuracy and reliability in GIS deliverables, particularly across sectors such as urban planning, transportation, infrastructure, utilities, environmental management, and e-governance.
+At Digital Indian Business Solutions, we take pride in consistently achieving over 80% accuracy in GIS data processing, feature extraction, mapping, and quality-controlled deliverables. This is supported by our robust quality assurance framework, experienced professionals, and the use of advanced GIS tools and technologies.</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>Suvosree Roy</v>
+      </c>
+      <c r="B27" t="str">
+        <v>info@digitalindian.co.in</v>
+      </c>
+      <c r="C27" t="str">
+        <v>9030080679</v>
+      </c>
+      <c r="D27" t="str">
+        <v>Cadastral Datasets, Land Record Verification, Data Cleaning, Data Correction, Others</v>
+      </c>
+      <c r="E27" t="str" xml:space="preserve">
+        <v xml:space="preserve">I hope this message finds you well.
+I am writing on behalf of DigitalIndian Business Solutions Pvt. Ltd., a growing technology and consulting firm specializing in Geographic Information Systems (GIS), data management, and IT-enabled services.
+With the GIS industry witnessing rapid growth in India, the demand for high-precision spatial data, mapping, and decision-support solutions continues to rise. We understand the critical importance of accuracy and reliability in GIS deliverables, particularly across sectors such as urban planning, transportation, infrastructure, utilities, environmental management, and e-governance.
+At Digital Indian Business Solutions, we take pride in consistently achieving over 80% accuracy in GIS data processing, feature extraction, mapping, and quality-controlled deliverables. This is supported by our robust quality assurance framework, experienced professionals, and the use of advanced GIS tools and technologies.</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>Sophie Lane</v>
+      </c>
+      <c r="B28" t="str">
+        <v>sophie@sendproud.com</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2155394452</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v>Hi, I’m Sophie! I tried to find you on LinkedIn but couldn’t, so I’m reaching out here. I help businesses book meetings, drive traffic, and generate user sign ups through targeted outreach using my extensive private network, built over 12+ years, with access to over 100 million contacts. We’ll have a quick call to set a clear goal for your business, and I’ll personally work to make sure we reach it. You choose the result you want, whether that’s booked meetings, website traffic, user sign ups, or another measurable outcome, and if I fall short by even one, I’ll refund your money in full. Schedule a time with me here: https://calendly.com/sendproud/30min</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>Sophie Lane</v>
+      </c>
+      <c r="B29" t="str">
+        <v>sophie@sendproud.com</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2155394452</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E29"/>
   </ignoredErrors>
 </worksheet>
 </file>